--- a/data/trans_camb/IP16B98-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B98-Habitat-trans_camb.xlsx
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,66</t>
+          <t>0,0; 37,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 43,42</t>
+          <t>-16,08; 49,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 29,41</t>
+          <t>-5,19; 30,3</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,42</t>
+          <t>0,0; 60,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 77,46</t>
+          <t>-16,12; 110,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 42,26</t>
+          <t>-5,38; 46,29</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 0,0</t>
+          <t>-57,23; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 36,02</t>
+          <t>-23,25; 37,17</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 0,0</t>
+          <t>-57,23; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 56,23</t>
+          <t>-25,88; 58,04</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-62,56; 0,0</t>
+          <t>-63,4; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,15</t>
+          <t>0,0; 45,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 30,5</t>
+          <t>-12,98; 26,59</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,56; 0,0</t>
+          <t>-63,4; 0,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,33</t>
+          <t>0,0; 82,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 43,9</t>
+          <t>-13,07; 39,12</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 19,86</t>
+          <t>-3,8; 19,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 16,6</t>
+          <t>-10,27; 16,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 12,75</t>
+          <t>-4,84; 12,24</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 25,59</t>
+          <t>-4,0; 25,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 19,74</t>
+          <t>-10,9; 19,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 15,21</t>
+          <t>-4,87; 14,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B98-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B98-Habitat-trans_camb.xlsx
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,72</t>
+          <t>0,0; 46,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 49,28</t>
+          <t>-15,93; 46,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 30,3</t>
+          <t>-5,92; 29,11</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,56</t>
+          <t>0,0; 86,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 110,61</t>
+          <t>-15,98; 86,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 46,29</t>
+          <t>-6,24; 43,45</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 0,0</t>
+          <t>-57,01; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 37,17</t>
+          <t>-22,76; 35,96</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 0,0</t>
+          <t>-57,01; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 58,04</t>
+          <t>-24,47; 55,5</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 0,0</t>
+          <t>-61,42; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,32</t>
+          <t>0,0; 45,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 26,59</t>
+          <t>-12,83; 32,44</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 0,0</t>
+          <t>-61,42; 0,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,87</t>
+          <t>0,0; 83,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 39,12</t>
+          <t>-13,0; 47,9</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 19,37</t>
+          <t>-2,67; 19,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 16,64</t>
+          <t>-10,52; 15,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 12,24</t>
+          <t>-5,36; 12,75</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 25,06</t>
+          <t>-2,67; 24,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 19,98</t>
+          <t>-11,2; 18,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 14,21</t>
+          <t>-5,57; 15,08</t>
         </is>
       </c>
     </row>
